--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_real_estate_general_diversified.xlsx
@@ -588,76 +588,79 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.003</v>
+        <v>-0.0252</v>
       </c>
       <c r="E2">
-        <v>0.162</v>
+        <v>-0.0818</v>
       </c>
       <c r="G2">
-        <v>0.3512820512820513</v>
+        <v>0.2715877437325905</v>
       </c>
       <c r="H2">
-        <v>0.3512820512820513</v>
+        <v>0.2715877437325905</v>
       </c>
       <c r="I2">
-        <v>0.4769230769230769</v>
+        <v>0.1657381615598886</v>
       </c>
       <c r="J2">
-        <v>0.4309650349650349</v>
+        <v>0.1432081302228412</v>
       </c>
       <c r="K2">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="L2">
-        <v>1.91025641025641</v>
+        <v>2.311977715877438</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04978165938864629</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.6867469879518072</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04978165938864629</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.6867469879518072</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.5679999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="V2">
-        <v>0.03283236994219653</v>
+        <v>0.01179039301310044</v>
       </c>
       <c r="W2">
-        <v>0.06008064516129032</v>
+        <v>0.06311787072243345</v>
       </c>
       <c r="X2">
-        <v>0.08381299205324118</v>
+        <v>0.09866260751625905</v>
       </c>
       <c r="Y2">
-        <v>-0.02373234689195085</v>
+        <v>-0.0355447367938256</v>
       </c>
       <c r="Z2">
-        <v>0.03158662023163522</v>
+        <v>0.02790300015544847</v>
       </c>
       <c r="AA2">
-        <v>0.01361272889255395</v>
+        <v>0.003995936479869423</v>
       </c>
       <c r="AB2">
-        <v>0.08381299205324118</v>
+        <v>0.09866260751625905</v>
       </c>
       <c r="AC2">
-        <v>-0.07020026316068723</v>
+        <v>-0.09466667103638962</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.5679999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03394692804207507</v>
+        <v>-0.01193106495802033</v>
       </c>
       <c r="AK2">
-        <v>-0.02207368257422664</v>
+        <v>-0.01078705553335997</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.363</v>
+        <v>-0.001</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.506631299734748</v>
+        <v>-2.125984251968504</v>
       </c>
       <c r="AQ2">
-        <v>-1.024793388429752</v>
+        <v>-119</v>
       </c>
     </row>
     <row r="3">
@@ -716,76 +719,79 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.003</v>
+        <v>-0.0252</v>
       </c>
       <c r="E3">
-        <v>0.162</v>
+        <v>-0.0818</v>
       </c>
       <c r="G3">
-        <v>0.3512820512820513</v>
+        <v>0.2715877437325905</v>
       </c>
       <c r="H3">
-        <v>0.3512820512820513</v>
+        <v>0.2715877437325905</v>
       </c>
       <c r="I3">
-        <v>0.4769230769230769</v>
+        <v>0.1657381615598886</v>
       </c>
       <c r="J3">
-        <v>0.4309650349650349</v>
+        <v>0.1432081302228412</v>
       </c>
       <c r="K3">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="L3">
-        <v>1.91025641025641</v>
+        <v>2.311977715877438</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04978165938864629</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6867469879518072</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.14</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04978165938864629</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6867469879518072</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.5679999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="V3">
-        <v>0.03283236994219653</v>
+        <v>0.01179039301310044</v>
       </c>
       <c r="W3">
-        <v>0.06008064516129032</v>
+        <v>0.06311787072243345</v>
       </c>
       <c r="X3">
-        <v>0.08381299205324118</v>
+        <v>0.09866260751625905</v>
       </c>
       <c r="Y3">
-        <v>-0.02373234689195085</v>
+        <v>-0.0355447367938256</v>
       </c>
       <c r="Z3">
-        <v>0.03158662023163522</v>
+        <v>0.02790300015544847</v>
       </c>
       <c r="AA3">
-        <v>0.01361272889255395</v>
+        <v>0.003995936479869423</v>
       </c>
       <c r="AB3">
-        <v>0.08381299205324118</v>
+        <v>0.09866260751625905</v>
       </c>
       <c r="AC3">
-        <v>-0.07020026316068723</v>
+        <v>-0.09466667103638962</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.5679999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03394692804207507</v>
+        <v>-0.01193106495802033</v>
       </c>
       <c r="AK3">
-        <v>-0.02207368257422664</v>
+        <v>-0.01078705553335997</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.363</v>
+        <v>-0.001</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.506631299734748</v>
+        <v>-2.125984251968504</v>
       </c>
       <c r="AQ3">
-        <v>-1.024793388429752</v>
+        <v>-119</v>
       </c>
     </row>
   </sheetData>
